--- a/countries/se-m/2026-2029.xlsx
+++ b/countries/se-m/2026-2029.xlsx
@@ -62659,10 +62659,10 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O441" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U441" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6527</v>
+        <v>6526</v>
       </c>
     </row>
     <row r="16">
